--- a/test_data/WTA Calculator - Corporate Rate Finder/WTA Calculator - Corporate Rate Finder_Test_Cases.xlsx
+++ b/test_data/WTA Calculator - Corporate Rate Finder/WTA Calculator - Corporate Rate Finder_Test_Cases.xlsx
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Clicking Print opened a print-preview tab at 'https://regpluswta.api.kaz.com.bd/api/Print/Index?fileName=7ea34f91-eba3-4185-bc19-0eb152c8d957.text'.</t>
+          <t>Clicking Print opened a print-preview tab at 'https://regpluswta.api.kaz.com.bd/api/Print/Index?fileName=f5f65eb5-2aac-449c-ba59-96a7768ec6ae.text'.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">

--- a/test_data/WTA Calculator - Corporate Rate Finder/WTA Calculator - Corporate Rate Finder_Test_Cases.xlsx
+++ b/test_data/WTA Calculator - Corporate Rate Finder/WTA Calculator - Corporate Rate Finder_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -906,17 +914,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>The UI correctly displayed '55%', matching the live API's independent HeadlineRate value for Bangladesh/2024.</t>
+          <t>The UI table did not match the independently-fetched API rate (expected 55%, table='Year\n\t\nType\n\t\nBangladesh\n\n\n2024\n\t\nHeadline\n\t\n27.5%').</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The UI rate cell matches the independently-fetched API HeadlineRate</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] The UI rate cell matches the independently-fetched API HeadlineRate</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1023,17 +1031,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>The table correctly rendered Australia/2024 with no rate value, reflecting the real, confirmed data gap rather than fabricating a figure.</t>
+          <t>The table did not render the known data-gap row as expected (body='2024\n\t\nHeadline\n\t\n30%').</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Table renders Year/Type with an empty rate cell for a known data gap</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] Table renders Year/Type with an empty rate cell for a known data gap</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1090,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>'Show More' switched to the expanded table layout while preserving the correct rate value.</t>
+          <t>The expanded table did not preserve the expected rate value (body='Year\tType\t\nBangladesh\n\n2024\tHeadline\t\n27.5%\n\n\xa0\tFinancial institutions\t\n40%\n\n\xa0\tTelecommunication\t\n45%\n\n\xa0\tTobacco company\t\n45%\n\n\xa0\t\xa0\t\xa0').</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The expanded table still shows the 55% rate</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] The expanded table still shows the 55% rate</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1141,17 +1149,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Bangladesh' opened the 'Corporate rate details' modal showing the matching 55% rate, confirming this is a same-page modal rather than a new page.</t>
+          <t>The rate details modal did not open with the expected content (modal_text='Corporate rate details for Bangladesh\nExport:\nTax Year\tType\tRate\tFootnote\n01 July 2024 to 30 June 2025\tHeadline\t\n27.5%\n\t\n\xa0\tFinancial institutions\t\n40%\n\t\n\xa0\tTelecommunication\t\n45%\n\t\n\xa0\tTobacco company\t\n45%\n\t').</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[PASS] The rate details modal opens with the correct title and rate</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>[FAIL] The rate details modal opens with the correct title and rate</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1267,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>The Excel export downloaded 'BD_CorpTaxRate_English.xlsx' (2896 bytes) successfully.</t>
+          <t>The Excel export downloaded 'BD_CorpTaxRate_English.xlsx' (2897 bytes) successfully.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1318,7 +1326,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Clicking Print opened a print-preview tab at 'https://regpluswta.api.kaz.com.bd/api/Print/Index?fileName=f5f65eb5-2aac-449c-ba59-96a7768ec6ae.text'.</t>
+          <t>Clicking Print opened a print-preview tab at 'https://regplusrcwtaapi.reganalytics.com/api/Print/Index?fileName=6e472ecc-f515-4e06-a9d5-7ed0158d0a61.text'.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1495,7 +1503,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>The modal's Export icon correctly downloaded 'BD_CorpTaxRate_English.xlsx' (2966 bytes).</t>
+          <t>The modal's Export icon correctly downloaded 'BD_CorpTaxRate_English.xlsx' (3063 bytes).</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
